--- a/artfynd/A 31875-2025 artfynd.xlsx
+++ b/artfynd/A 31875-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>75834911</v>
+        <v>74092611</v>
       </c>
       <c r="B2" t="n">
-        <v>56538</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57874</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103020</v>
+        <v>100001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -713,8 +708,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -727,10 +730,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>564969.2169858349</v>
+        <v>564960</v>
       </c>
       <c r="R2" t="n">
-        <v>6666360.947895032</v>
+        <v>6666371</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -757,22 +760,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-01-25</t>
+          <t>2018-11-11</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>2018-11-11</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
           <t>12:00</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>2019-01-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,52 +790,51 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Neo Stratospey</t>
+          <t>Kjell Gustafsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Neo Stratospey</t>
+          <t>Kjell Gustafsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>75849905</v>
+        <v>73263768</v>
       </c>
       <c r="B3" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
@@ -847,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>564969.2169858349</v>
+        <v>564960</v>
       </c>
       <c r="R3" t="n">
-        <v>6666360.947895032</v>
+        <v>6666371</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -877,22 +879,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-01-26</t>
+          <t>2018-09-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-01-26</t>
+          <t>2018-09-24</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,44 +909,39 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Neo Stratospey</t>
+          <t>Kjell Gustafsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Neo Stratospey</t>
+          <t>Kjell Gustafsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>75849900</v>
+        <v>106148527</v>
       </c>
       <c r="B4" t="n">
-        <v>57007</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58067</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103042</v>
+        <v>100090</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Nucifraga caryocatactes</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -954,27 +951,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Myggbo, Avesta, Dlr</t>
+          <t>Myggbo Avesta, Avesta, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>564969.2169858349</v>
+        <v>565051</v>
       </c>
       <c r="R4" t="n">
-        <v>6666360.947895032</v>
+        <v>6666345</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1001,22 +998,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2019-01-26</t>
+          <t>2023-01-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2019-01-26</t>
+          <t>2023-01-24</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Hördes några gånger bortanför elledningen.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,27 +1033,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Neo Stratospey</t>
+          <t>Per-Inge Josefsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Neo Stratospey</t>
+          <t>Per-Inge Josefsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>76545253</v>
+        <v>106609289</v>
       </c>
       <c r="B5" t="n">
-        <v>57064</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58067</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1059,21 +1056,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103055</v>
+        <v>100090</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Nucifraga caryocatactes</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1095,13 +1092,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>564969.2169858349</v>
+        <v>564956</v>
       </c>
       <c r="R5" t="n">
-        <v>6666360.947895032</v>
+        <v>6666371</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1125,22 +1122,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2019-03-23</t>
+          <t>2023-02-11</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2019-03-23</t>
+          <t>2023-02-11</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Vid matningen O gångvägen längs kraftledningen</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,49 +1157,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Neo Stratospey</t>
+          <t>Alf Isaksson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Neo Stratospey</t>
+          <t>Alf Isaksson, Brith Isaksson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>80449590</v>
+        <v>73750811</v>
       </c>
       <c r="B6" t="n">
-        <v>56806</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57945</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103001</v>
+        <v>100110</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1206,10 +1203,14 @@
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1219,10 +1220,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564969.2169858349</v>
+        <v>564960</v>
       </c>
       <c r="R6" t="n">
-        <v>6666360.947895032</v>
+        <v>6666371</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1249,22 +1250,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2019-10-15</t>
+          <t>2018-10-28</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2019-10-15</t>
+          <t>2018-10-28</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1279,27 +1280,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Neo Stratospey</t>
+          <t>Kjell Gustafsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Neo Stratospey</t>
+          <t>Kjell Gustafsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>82107046</v>
+        <v>74112873</v>
       </c>
       <c r="B7" t="n">
-        <v>56812</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57794</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1307,26 +1303,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102999</v>
+        <v>102621</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1343,10 +1339,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564969.2169858349</v>
+        <v>564960</v>
       </c>
       <c r="R7" t="n">
-        <v>6666360.947895032</v>
+        <v>6666371</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1373,22 +1369,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2020-02-09</t>
+          <t>2018-11-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2020-02-09</t>
+          <t>2018-11-12</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1403,15 +1399,2136 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
+          <t>Kjell Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Kjell Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>77596540</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58497</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>102990</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Prunella modularis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Myggbo, Avesta, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>564969</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6666361</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Avesta</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Avesta</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2019-05-07</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2019-05-07</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Neo Stratospey</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Neo Stratospey</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>73318413</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58393</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>102999</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Björktrast</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Turdus pilaris</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Myggbo, Avesta, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>564960</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6666371</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Avesta</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Avesta</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2018-09-29</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2018-09-29</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kjell Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kjell Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>82107046</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58393</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>102999</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Björktrast</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Turdus pilaris</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Myggbo, Avesta, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>564969</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6666361</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Avesta</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Avesta</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2020-02-09</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2020-02-09</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Neo Stratospey</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Neo Stratospey</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>80449590</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58388</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Myggbo, Avesta, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>564969</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6666361</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Avesta</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Avesta</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2019-10-15</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2019-10-15</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Neo Stratospey</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Neo Stratospey</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>74681209</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Myggbo, Avesta, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>564960</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6666371</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Avesta</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Avesta</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2018-11-25</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2018-11-25</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Kjell Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Kjell Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>75802876</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Myggbo, Avesta, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>564969</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6666361</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Avesta</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Avesta</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2019-01-22</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2019-01-22</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Födosökande.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Neo Stratospey</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Neo Stratospey</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>73429369</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Myggbo, Avesta, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>564960</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6666371</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Avesta</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Avesta</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2018-10-07</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2018-10-07</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Kjell Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Kjell Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>75834911</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Myggbo, Avesta, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>564969</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6666361</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Avesta</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Avesta</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2019-01-25</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2019-01-25</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Neo Stratospey</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Neo Stratospey</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>73429361</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Myggbo, Avesta, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>564960</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6666371</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Avesta</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Avesta</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2018-10-07</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2018-10-07</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Kjell Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Kjell Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>75849905</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Myggbo, Avesta, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>564969</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6666361</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Avesta</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Avesta</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2019-01-26</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2019-01-26</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Neo Stratospey</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Neo Stratospey</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>106148428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Myggbo Avesta, Avesta, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>565051</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6666345</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Avesta</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Avesta</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2023-01-24</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2023-01-24</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Per-Inge Josefsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Per-Inge Josefsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>75849900</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58602</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Myggbo, Avesta, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>564969</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6666361</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Avesta</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Avesta</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2019-01-26</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2019-01-26</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Neo Stratospey</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Neo Stratospey</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>73318443</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Myggbo, Avesta, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>564960</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6666371</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Avesta</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Avesta</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2018-09-29</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2018-09-29</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Kjell Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Kjell Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>77596664</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Myggbo, Avesta, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>564969</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6666361</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Avesta</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Avesta</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2019-05-07</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2019-05-07</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Neo Stratospey</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Neo Stratospey</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>73429436</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Myggbo, Avesta, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>564960</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6666371</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Avesta</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Avesta</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2018-10-07</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2018-10-07</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Kjell Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Kjell Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>76545253</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Myggbo, Avesta, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>564969</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6666361</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Avesta</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Avesta</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2019-03-23</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2019-03-23</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Neo Stratospey</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Neo Stratospey</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>106148495</v>
+      </c>
+      <c r="B24" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Myggbo Avesta, Avesta, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>565051</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6666345</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Avesta</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Avesta</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2023-01-24</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2023-01-24</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Per-Inge Josefsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Per-Inge Josefsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>80752629</v>
+      </c>
+      <c r="B25" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>V Myggbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>564210</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6666016</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Avesta</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Avesta</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2019-08-23</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2019-08-23</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Felicia Alriksson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Felicia Alriksson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31875-2025 artfynd.xlsx
+++ b/artfynd/A 31875-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -799,6 +804,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74092611</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -918,6 +928,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73263768</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1042,6 +1057,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106148527</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1166,6 +1186,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106609289</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1289,6 +1314,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73750811</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1408,6 +1438,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74112873</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1527,6 +1562,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77596540</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1646,6 +1686,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73318413</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1765,6 +1810,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82107046</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1884,6 +1934,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80449590</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2003,6 +2058,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74681209</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2123,6 +2183,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75802876</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2242,6 +2307,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73429369</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2361,6 +2431,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75834911</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2480,6 +2555,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73429361</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2595,6 +2675,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75849905</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2714,6 +2799,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106148428</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2833,6 +2923,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75849900</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2952,6 +3047,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73318443</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3075,6 +3175,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77596664</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3194,6 +3299,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73429436</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3313,6 +3423,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76545253</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3432,6 +3547,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106148495</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3529,8 +3649,39 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80752629</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>